--- a/input/mapping/067. OCB_GOLD_TCKH_AR_DIM_HOP.xlsx
+++ b/input/mapping/067. OCB_GOLD_TCKH_AR_DIM_HOP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1945" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB4AD0EA-BA29-40B9-953B-86B45C83C02B}"/>
+  <xr:revisionPtr revIDLastSave="1955" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C72B83C-F450-49CD-A925-552B0C0CF60D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="15" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -250,23 +250,6 @@
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
--- =============================================================================
--- AR_DIM
--- Sửa: sat_lc_cls đổi ref_type = 'CATEGORY' -&gt; ref_type = 'LC_TYPES'
--- =============================================================================
-CREATE TABLE IF NOT EXISTS AR_DIM (
-    AR_DW_ID        STRING,
-    AR_DIM_ID       STRING,
-    AR_ID           STRING,
-    AR_NM           STRING,
-    AR_TP_ID        STRING,
-    AR_TP           STRING,
-    AR_LC_ST_TP     STRING,
-    AR_TERM_TP      STRING,
-    AR_TP_NM        STRING,
-    PPN_TM          TIMESTAMP
-)
-USING DELTA;
 TRUNCATE TABLE AR_DIM;
 INSERT INTO AR_DIM
 WITH
@@ -672,8 +655,7 @@
     NULL                AS AR_TERM_TP,
     AR_TP_NM,
     CURRENT_TIMESTAMP() AS PPN_TM
-FROM cte_dedup
-;</t>
+FROM cte_dedup</t>
   </si>
   <si>
     <t xml:space="preserve">    </t>
@@ -3171,7 +3153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="234">
+  <cellXfs count="233">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3573,6 +3555,213 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="14" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="14" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3597,214 +3786,6 @@
     <xf numFmtId="0" fontId="27" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="14" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="14" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
     </xf>
@@ -3826,7 +3807,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -4193,15 +4174,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="30" customHeight="1">
-      <c r="A1" s="159" t="s">
+      <c r="A1" s="151" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="160"/>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="160"/>
-      <c r="G1" s="160"/>
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
+      <c r="G1" s="152"/>
       <c r="H1" s="119"/>
       <c r="I1" s="117"/>
       <c r="J1" s="39"/>
@@ -4245,12 +4226,12 @@
       <c r="AV1" s="39"/>
     </row>
     <row r="2" spans="1:48">
-      <c r="A2" s="156" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="156"/>
-      <c r="C2" s="156"/>
-      <c r="D2" s="161" t="s">
+      <c r="A2" s="148" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="148"/>
+      <c r="C2" s="148"/>
+      <c r="D2" s="153" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="122" t="s">
@@ -4265,10 +4246,10 @@
       <c r="I2" s="118"/>
     </row>
     <row r="3" spans="1:48">
-      <c r="A3" s="157"/>
-      <c r="B3" s="157"/>
-      <c r="C3" s="157"/>
-      <c r="D3" s="162"/>
+      <c r="A3" s="149"/>
+      <c r="B3" s="149"/>
+      <c r="C3" s="149"/>
+      <c r="D3" s="154"/>
       <c r="E3" s="122" t="s">
         <v>6</v>
       </c>
@@ -4282,10 +4263,10 @@
       <c r="I3" s="118"/>
     </row>
     <row r="4" spans="1:48">
-      <c r="A4" s="157"/>
-      <c r="B4" s="157"/>
-      <c r="C4" s="157"/>
-      <c r="D4" s="162"/>
+      <c r="A4" s="149"/>
+      <c r="B4" s="149"/>
+      <c r="C4" s="149"/>
+      <c r="D4" s="154"/>
       <c r="E4" s="122" t="s">
         <v>9</v>
       </c>
@@ -4299,10 +4280,10 @@
       <c r="I4" s="118"/>
     </row>
     <row r="5" spans="1:48" ht="18.75" customHeight="1">
-      <c r="A5" s="157"/>
-      <c r="B5" s="157"/>
-      <c r="C5" s="157"/>
-      <c r="D5" s="162"/>
+      <c r="A5" s="149"/>
+      <c r="B5" s="149"/>
+      <c r="C5" s="149"/>
+      <c r="D5" s="154"/>
       <c r="E5" s="122" t="s">
         <v>12</v>
       </c>
@@ -4316,10 +4297,10 @@
       <c r="I5" s="118"/>
     </row>
     <row r="6" spans="1:48">
-      <c r="A6" s="157"/>
-      <c r="B6" s="157"/>
-      <c r="C6" s="157"/>
-      <c r="D6" s="162"/>
+      <c r="A6" s="149"/>
+      <c r="B6" s="149"/>
+      <c r="C6" s="149"/>
+      <c r="D6" s="154"/>
       <c r="E6" s="122" t="s">
         <v>15</v>
       </c>
@@ -4331,10 +4312,10 @@
       </c>
     </row>
     <row r="7" spans="1:48">
-      <c r="A7" s="157"/>
-      <c r="B7" s="157"/>
-      <c r="C7" s="157"/>
-      <c r="D7" s="162"/>
+      <c r="A7" s="149"/>
+      <c r="B7" s="149"/>
+      <c r="C7" s="149"/>
+      <c r="D7" s="154"/>
       <c r="E7" s="122" t="s">
         <v>18</v>
       </c>
@@ -4351,10 +4332,10 @@
       <c r="L7" s="124"/>
     </row>
     <row r="8" spans="1:48" ht="19.5" customHeight="1">
-      <c r="A8" s="157"/>
-      <c r="B8" s="157"/>
-      <c r="C8" s="157"/>
-      <c r="D8" s="162"/>
+      <c r="A8" s="149"/>
+      <c r="B8" s="149"/>
+      <c r="C8" s="149"/>
+      <c r="D8" s="154"/>
       <c r="E8" s="122" t="s">
         <v>21</v>
       </c>
@@ -4371,10 +4352,10 @@
       <c r="L8" s="124"/>
     </row>
     <row r="9" spans="1:48">
-      <c r="A9" s="157"/>
-      <c r="B9" s="157"/>
-      <c r="C9" s="157"/>
-      <c r="D9" s="162"/>
+      <c r="A9" s="149"/>
+      <c r="B9" s="149"/>
+      <c r="C9" s="149"/>
+      <c r="D9" s="154"/>
       <c r="E9" s="122" t="s">
         <v>24</v>
       </c>
@@ -4389,10 +4370,10 @@
       <c r="L9" s="124"/>
     </row>
     <row r="10" spans="1:48" ht="18.75" customHeight="1">
-      <c r="A10" s="157"/>
-      <c r="B10" s="157"/>
-      <c r="C10" s="157"/>
-      <c r="D10" s="162"/>
+      <c r="A10" s="149"/>
+      <c r="B10" s="149"/>
+      <c r="C10" s="149"/>
+      <c r="D10" s="154"/>
       <c r="E10" s="122" t="s">
         <v>26</v>
       </c>
@@ -4409,10 +4390,10 @@
       <c r="L10" s="124"/>
     </row>
     <row r="11" spans="1:48">
-      <c r="A11" s="157"/>
-      <c r="B11" s="157"/>
-      <c r="C11" s="157"/>
-      <c r="D11" s="162"/>
+      <c r="A11" s="149"/>
+      <c r="B11" s="149"/>
+      <c r="C11" s="149"/>
+      <c r="D11" s="154"/>
       <c r="E11" s="122" t="s">
         <v>29</v>
       </c>
@@ -4429,10 +4410,10 @@
       <c r="L11" s="124"/>
     </row>
     <row r="12" spans="1:48">
-      <c r="A12" s="157"/>
-      <c r="B12" s="157"/>
-      <c r="C12" s="157"/>
-      <c r="D12" s="162"/>
+      <c r="A12" s="149"/>
+      <c r="B12" s="149"/>
+      <c r="C12" s="149"/>
+      <c r="D12" s="154"/>
       <c r="E12" s="122" t="s">
         <v>32</v>
       </c>
@@ -4449,10 +4430,10 @@
       <c r="L12" s="124"/>
     </row>
     <row r="13" spans="1:48">
-      <c r="A13" s="157"/>
-      <c r="B13" s="157"/>
-      <c r="C13" s="157"/>
-      <c r="D13" s="162"/>
+      <c r="A13" s="149"/>
+      <c r="B13" s="149"/>
+      <c r="C13" s="149"/>
+      <c r="D13" s="154"/>
       <c r="E13" s="122" t="s">
         <v>35</v>
       </c>
@@ -4469,10 +4450,10 @@
       <c r="L13" s="124"/>
     </row>
     <row r="14" spans="1:48">
-      <c r="A14" s="157"/>
-      <c r="B14" s="157"/>
-      <c r="C14" s="157"/>
-      <c r="D14" s="162"/>
+      <c r="A14" s="149"/>
+      <c r="B14" s="149"/>
+      <c r="C14" s="149"/>
+      <c r="D14" s="154"/>
       <c r="E14" s="122" t="s">
         <v>38</v>
       </c>
@@ -4489,10 +4470,10 @@
       <c r="L14" s="124"/>
     </row>
     <row r="15" spans="1:48">
-      <c r="A15" s="157"/>
-      <c r="B15" s="157"/>
-      <c r="C15" s="157"/>
-      <c r="D15" s="162"/>
+      <c r="A15" s="149"/>
+      <c r="B15" s="149"/>
+      <c r="C15" s="149"/>
+      <c r="D15" s="154"/>
       <c r="E15" s="122" t="s">
         <v>41</v>
       </c>
@@ -4509,10 +4490,10 @@
       <c r="L15" s="124"/>
     </row>
     <row r="16" spans="1:48">
-      <c r="A16" s="157"/>
-      <c r="B16" s="157"/>
-      <c r="C16" s="157"/>
-      <c r="D16" s="162"/>
+      <c r="A16" s="149"/>
+      <c r="B16" s="149"/>
+      <c r="C16" s="149"/>
+      <c r="D16" s="154"/>
       <c r="E16" s="122" t="s">
         <v>44</v>
       </c>
@@ -4529,10 +4510,10 @@
       <c r="L16" s="124"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="158"/>
-      <c r="B17" s="158"/>
-      <c r="C17" s="158"/>
-      <c r="D17" s="163"/>
+      <c r="A17" s="150"/>
+      <c r="B17" s="150"/>
+      <c r="C17" s="150"/>
+      <c r="D17" s="155"/>
       <c r="E17" s="122" t="s">
         <v>47</v>
       </c>
@@ -4560,10 +4541,10 @@
       <c r="L18" s="124"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="155" t="s">
+      <c r="A19" s="147" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="155"/>
+      <c r="B19" s="147"/>
       <c r="C19" s="145"/>
       <c r="F19" s="123"/>
       <c r="G19" s="123"/>
@@ -4575,7 +4556,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="140"/>
-      <c r="B20" s="225" t="s">
+      <c r="B20" s="224" t="s">
         <v>51</v>
       </c>
       <c r="C20" s="145"/>
@@ -4589,7 +4570,7 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="141"/>
-      <c r="B21" s="225" t="s">
+      <c r="B21" s="224" t="s">
         <v>52</v>
       </c>
       <c r="C21" s="145"/>
@@ -4603,7 +4584,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="142"/>
-      <c r="B22" s="225" t="s">
+      <c r="B22" s="224" t="s">
         <v>53</v>
       </c>
       <c r="C22" s="145"/>
@@ -4615,14 +4596,14 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="143"/>
-      <c r="B23" s="225" t="s">
+      <c r="B23" s="224" t="s">
         <v>54</v>
       </c>
       <c r="C23" s="145"/>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="144"/>
-      <c r="B24" s="225" t="s">
+      <c r="B24" s="224" t="s">
         <v>55</v>
       </c>
       <c r="C24" s="145"/>
@@ -4640,10 +4621,10 @@
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="226" t="s">
-        <v>1</v>
-      </c>
-      <c r="B27" s="226" t="s">
+      <c r="A27" s="225" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="225" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4889,13 +4870,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="41.25" customHeight="1">
-      <c r="A1" s="207" t="s">
+      <c r="A1" s="199" t="s">
         <v>354</v>
       </c>
-      <c r="B1" s="208"/>
-      <c r="C1" s="208"/>
-      <c r="D1" s="208"/>
-      <c r="E1" s="208"/>
+      <c r="B1" s="200"/>
+      <c r="C1" s="200"/>
+      <c r="D1" s="200"/>
+      <c r="E1" s="200"/>
     </row>
     <row r="2" spans="1:5" ht="18.75">
       <c r="A2" s="61" t="s">
@@ -4937,13 +4918,13 @@
       <c r="E4" s="63"/>
     </row>
     <row r="5" spans="1:5" ht="18.75">
-      <c r="A5" s="208" t="s">
+      <c r="A5" s="200" t="s">
         <v>357</v>
       </c>
-      <c r="B5" s="208"/>
-      <c r="C5" s="208"/>
-      <c r="D5" s="208"/>
-      <c r="E5" s="208"/>
+      <c r="B5" s="200"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="200"/>
+      <c r="E5" s="200"/>
     </row>
     <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="61" t="s">
@@ -5076,14 +5057,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A1" s="209" t="s">
+      <c r="A1" s="201" t="s">
         <v>364</v>
       </c>
-      <c r="B1" s="210"/>
-      <c r="C1" s="210"/>
-      <c r="D1" s="210"/>
-      <c r="E1" s="210"/>
-      <c r="F1" s="210"/>
+      <c r="B1" s="202"/>
+      <c r="C1" s="202"/>
+      <c r="D1" s="202"/>
+      <c r="E1" s="202"/>
+      <c r="F1" s="202"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="66" t="s">
@@ -5092,10 +5073,10 @@
       <c r="B2" s="66" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="211" t="s">
+      <c r="C2" s="203" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="212"/>
+      <c r="D2" s="204"/>
       <c r="E2" s="66" t="s">
         <v>71</v>
       </c>
@@ -5110,8 +5091,8 @@
       <c r="B3" s="68" t="s">
         <v>365</v>
       </c>
-      <c r="C3" s="213"/>
-      <c r="D3" s="214"/>
+      <c r="C3" s="205"/>
+      <c r="D3" s="206"/>
       <c r="E3" s="68" t="s">
         <v>75</v>
       </c>
@@ -5128,13 +5109,13 @@
       <c r="F4" s="69"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="210" t="s">
+      <c r="A5" s="202" t="s">
         <v>367</v>
       </c>
-      <c r="B5" s="210"/>
-      <c r="C5" s="210"/>
-      <c r="D5" s="210"/>
-      <c r="E5" s="210"/>
+      <c r="B5" s="202"/>
+      <c r="C5" s="202"/>
+      <c r="D5" s="202"/>
+      <c r="E5" s="202"/>
       <c r="F5" s="70"/>
     </row>
     <row r="6" spans="1:6">
@@ -6394,14 +6375,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A1" s="215" t="s">
+      <c r="A1" s="207" t="s">
         <v>433</v>
       </c>
-      <c r="B1" s="216"/>
-      <c r="C1" s="216"/>
-      <c r="D1" s="216"/>
-      <c r="E1" s="216"/>
-      <c r="F1" s="216"/>
+      <c r="B1" s="208"/>
+      <c r="C1" s="208"/>
+      <c r="D1" s="208"/>
+      <c r="E1" s="208"/>
+      <c r="F1" s="208"/>
     </row>
     <row r="2" spans="1:6" ht="18.75">
       <c r="A2" s="60" t="s">
@@ -6410,10 +6391,10 @@
       <c r="B2" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="216" t="s">
+      <c r="C2" s="208" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="216"/>
+      <c r="D2" s="208"/>
       <c r="E2" s="60" t="s">
         <v>71</v>
       </c>
@@ -6430,13 +6411,13 @@
       <c r="F3" s="75"/>
     </row>
     <row r="4" spans="1:6" ht="18.75">
-      <c r="A4" s="216" t="s">
+      <c r="A4" s="208" t="s">
         <v>434</v>
       </c>
-      <c r="B4" s="216"/>
-      <c r="C4" s="216"/>
-      <c r="D4" s="216"/>
-      <c r="E4" s="216"/>
+      <c r="B4" s="208"/>
+      <c r="C4" s="208"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
       <c r="F4" s="76"/>
     </row>
     <row r="5" spans="1:6" ht="18.75">
@@ -7687,13 +7668,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.5" customHeight="1">
-      <c r="A1" s="217" t="s">
+      <c r="A1" s="209" t="s">
         <v>436</v>
       </c>
-      <c r="B1" s="218"/>
-      <c r="C1" s="218"/>
-      <c r="D1" s="218"/>
-      <c r="E1" s="218"/>
+      <c r="B1" s="210"/>
+      <c r="C1" s="210"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="210"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="81" t="s">
@@ -7728,13 +7709,13 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="219" t="s">
+      <c r="A4" s="211" t="s">
         <v>439</v>
       </c>
-      <c r="B4" s="220"/>
-      <c r="C4" s="220"/>
-      <c r="D4" s="220"/>
-      <c r="E4" s="221"/>
+      <c r="B4" s="212"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="212"/>
+      <c r="E4" s="213"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="81" t="s">
@@ -7850,13 +7831,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="47.25" customHeight="1">
-      <c r="A1" s="222" t="s">
+      <c r="A1" s="214" t="s">
         <v>443</v>
       </c>
-      <c r="B1" s="223"/>
-      <c r="C1" s="223"/>
-      <c r="D1" s="223"/>
-      <c r="E1" s="223"/>
+      <c r="B1" s="215"/>
+      <c r="C1" s="215"/>
+      <c r="D1" s="215"/>
+      <c r="E1" s="215"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="85" t="s">
@@ -7883,13 +7864,13 @@
       <c r="E3" s="86"/>
     </row>
     <row r="5" spans="1:5" ht="18.75">
-      <c r="A5" s="216" t="s">
+      <c r="A5" s="208" t="s">
         <v>444</v>
       </c>
-      <c r="B5" s="216"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="216"/>
-      <c r="E5" s="216"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="208"/>
+      <c r="E5" s="208"/>
     </row>
     <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="60" t="s">
@@ -8154,15 +8135,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="216" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
-      <c r="G1" s="149"/>
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="218"/>
     </row>
     <row r="2" spans="1:7" s="138" customFormat="1">
       <c r="A2" s="126" t="s">
@@ -8200,9 +8181,9 @@
       <c r="D3" s="131" t="s">
         <v>75</v>
       </c>
-      <c r="E3" s="150"/>
-      <c r="F3" s="150"/>
-      <c r="G3" s="151"/>
+      <c r="E3" s="219"/>
+      <c r="F3" s="219"/>
+      <c r="G3" s="220"/>
     </row>
     <row r="4" spans="1:7" ht="30.75">
       <c r="A4" s="130">
@@ -8217,11 +8198,11 @@
       <c r="D4" s="131" t="s">
         <v>78</v>
       </c>
-      <c r="E4" s="150" t="s">
+      <c r="E4" s="219" t="s">
         <v>456</v>
       </c>
-      <c r="F4" s="150"/>
-      <c r="G4" s="151"/>
+      <c r="F4" s="219"/>
+      <c r="G4" s="220"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="130">
@@ -8236,22 +8217,22 @@
       <c r="D5" s="131" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="150" t="s">
+      <c r="E5" s="219" t="s">
         <v>459</v>
       </c>
-      <c r="F5" s="150"/>
-      <c r="G5" s="151"/>
+      <c r="F5" s="219"/>
+      <c r="G5" s="220"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="147" t="s">
+      <c r="A6" s="216" t="s">
         <v>460</v>
       </c>
-      <c r="B6" s="148"/>
-      <c r="C6" s="148"/>
-      <c r="D6" s="148"/>
-      <c r="E6" s="148"/>
-      <c r="F6" s="148"/>
-      <c r="G6" s="149"/>
+      <c r="B6" s="217"/>
+      <c r="C6" s="217"/>
+      <c r="D6" s="217"/>
+      <c r="E6" s="217"/>
+      <c r="F6" s="217"/>
+      <c r="G6" s="218"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="126" t="s">
@@ -8507,15 +8488,15 @@
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="152" t="s">
+      <c r="A18" s="221" t="s">
         <v>488</v>
       </c>
-      <c r="B18" s="153"/>
-      <c r="C18" s="153"/>
-      <c r="D18" s="153"/>
-      <c r="E18" s="153"/>
-      <c r="F18" s="153"/>
-      <c r="G18" s="154"/>
+      <c r="B18" s="222"/>
+      <c r="C18" s="222"/>
+      <c r="D18" s="222"/>
+      <c r="E18" s="222"/>
+      <c r="F18" s="222"/>
+      <c r="G18" s="223"/>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="130">
@@ -8748,15 +8729,15 @@
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="152" t="s">
+      <c r="A29" s="221" t="s">
         <v>488</v>
       </c>
-      <c r="B29" s="153"/>
-      <c r="C29" s="153"/>
-      <c r="D29" s="153"/>
-      <c r="E29" s="153"/>
-      <c r="F29" s="153"/>
-      <c r="G29" s="154"/>
+      <c r="B29" s="222"/>
+      <c r="C29" s="222"/>
+      <c r="D29" s="222"/>
+      <c r="E29" s="222"/>
+      <c r="F29" s="222"/>
+      <c r="G29" s="223"/>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="130">
@@ -8989,15 +8970,15 @@
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="147" t="s">
+      <c r="A40" s="216" t="s">
         <v>488</v>
       </c>
-      <c r="B40" s="148"/>
-      <c r="C40" s="148"/>
-      <c r="D40" s="148"/>
-      <c r="E40" s="148"/>
-      <c r="F40" s="148"/>
-      <c r="G40" s="149"/>
+      <c r="B40" s="217"/>
+      <c r="C40" s="217"/>
+      <c r="D40" s="217"/>
+      <c r="E40" s="217"/>
+      <c r="F40" s="217"/>
+      <c r="G40" s="218"/>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="130">
@@ -9230,15 +9211,15 @@
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="147" t="s">
+      <c r="A51" s="216" t="s">
         <v>488</v>
       </c>
-      <c r="B51" s="148"/>
-      <c r="C51" s="148"/>
-      <c r="D51" s="148"/>
-      <c r="E51" s="148"/>
-      <c r="F51" s="148"/>
-      <c r="G51" s="149"/>
+      <c r="B51" s="217"/>
+      <c r="C51" s="217"/>
+      <c r="D51" s="217"/>
+      <c r="E51" s="217"/>
+      <c r="F51" s="217"/>
+      <c r="G51" s="218"/>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="130">
@@ -9471,15 +9452,15 @@
       </c>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="147" t="s">
+      <c r="A62" s="216" t="s">
         <v>488</v>
       </c>
-      <c r="B62" s="148"/>
-      <c r="C62" s="148"/>
-      <c r="D62" s="148"/>
-      <c r="E62" s="148"/>
-      <c r="F62" s="148"/>
-      <c r="G62" s="149"/>
+      <c r="B62" s="217"/>
+      <c r="C62" s="217"/>
+      <c r="D62" s="217"/>
+      <c r="E62" s="217"/>
+      <c r="F62" s="217"/>
+      <c r="G62" s="218"/>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="130">
@@ -9712,15 +9693,15 @@
       </c>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="147" t="s">
+      <c r="A73" s="216" t="s">
         <v>488</v>
       </c>
-      <c r="B73" s="148"/>
-      <c r="C73" s="148"/>
-      <c r="D73" s="148"/>
-      <c r="E73" s="148"/>
-      <c r="F73" s="148"/>
-      <c r="G73" s="149"/>
+      <c r="B73" s="217"/>
+      <c r="C73" s="217"/>
+      <c r="D73" s="217"/>
+      <c r="E73" s="217"/>
+      <c r="F73" s="217"/>
+      <c r="G73" s="218"/>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="130">
@@ -9953,15 +9934,15 @@
       </c>
     </row>
     <row r="84" spans="1:7">
-      <c r="A84" s="147" t="s">
+      <c r="A84" s="216" t="s">
         <v>488</v>
       </c>
-      <c r="B84" s="148"/>
-      <c r="C84" s="148"/>
-      <c r="D84" s="148"/>
-      <c r="E84" s="148"/>
-      <c r="F84" s="148"/>
-      <c r="G84" s="149"/>
+      <c r="B84" s="217"/>
+      <c r="C84" s="217"/>
+      <c r="D84" s="217"/>
+      <c r="E84" s="217"/>
+      <c r="F84" s="217"/>
+      <c r="G84" s="218"/>
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="130">
@@ -10194,15 +10175,15 @@
       </c>
     </row>
     <row r="95" spans="1:7">
-      <c r="A95" s="147" t="s">
+      <c r="A95" s="216" t="s">
         <v>488</v>
       </c>
-      <c r="B95" s="148"/>
-      <c r="C95" s="148"/>
-      <c r="D95" s="148"/>
-      <c r="E95" s="148"/>
-      <c r="F95" s="148"/>
-      <c r="G95" s="149"/>
+      <c r="B95" s="217"/>
+      <c r="C95" s="217"/>
+      <c r="D95" s="217"/>
+      <c r="E95" s="217"/>
+      <c r="F95" s="217"/>
+      <c r="G95" s="218"/>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="130">
@@ -10435,15 +10416,15 @@
       </c>
     </row>
     <row r="106" spans="1:7">
-      <c r="A106" s="147" t="s">
+      <c r="A106" s="216" t="s">
         <v>488</v>
       </c>
-      <c r="B106" s="148"/>
-      <c r="C106" s="148"/>
-      <c r="D106" s="148"/>
-      <c r="E106" s="148"/>
-      <c r="F106" s="148"/>
-      <c r="G106" s="149"/>
+      <c r="B106" s="217"/>
+      <c r="C106" s="217"/>
+      <c r="D106" s="217"/>
+      <c r="E106" s="217"/>
+      <c r="F106" s="217"/>
+      <c r="G106" s="218"/>
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="130">
@@ -10676,15 +10657,15 @@
       </c>
     </row>
     <row r="117" spans="1:7">
-      <c r="A117" s="147" t="s">
+      <c r="A117" s="216" t="s">
         <v>488</v>
       </c>
-      <c r="B117" s="148"/>
-      <c r="C117" s="148"/>
-      <c r="D117" s="148"/>
-      <c r="E117" s="148"/>
-      <c r="F117" s="148"/>
-      <c r="G117" s="149"/>
+      <c r="B117" s="217"/>
+      <c r="C117" s="217"/>
+      <c r="D117" s="217"/>
+      <c r="E117" s="217"/>
+      <c r="F117" s="217"/>
+      <c r="G117" s="218"/>
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="130">
@@ -10917,15 +10898,15 @@
       </c>
     </row>
     <row r="128" spans="1:7">
-      <c r="A128" s="147" t="s">
+      <c r="A128" s="216" t="s">
         <v>488</v>
       </c>
-      <c r="B128" s="148"/>
-      <c r="C128" s="148"/>
-      <c r="D128" s="148"/>
-      <c r="E128" s="148"/>
-      <c r="F128" s="148"/>
-      <c r="G128" s="149"/>
+      <c r="B128" s="217"/>
+      <c r="C128" s="217"/>
+      <c r="D128" s="217"/>
+      <c r="E128" s="217"/>
+      <c r="F128" s="217"/>
+      <c r="G128" s="218"/>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="130">
@@ -11158,15 +11139,15 @@
       </c>
     </row>
     <row r="139" spans="1:7">
-      <c r="A139" s="147" t="s">
+      <c r="A139" s="216" t="s">
         <v>488</v>
       </c>
-      <c r="B139" s="148"/>
-      <c r="C139" s="148"/>
-      <c r="D139" s="148"/>
-      <c r="E139" s="148"/>
-      <c r="F139" s="148"/>
-      <c r="G139" s="149"/>
+      <c r="B139" s="217"/>
+      <c r="C139" s="217"/>
+      <c r="D139" s="217"/>
+      <c r="E139" s="217"/>
+      <c r="F139" s="217"/>
+      <c r="G139" s="218"/>
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="130">
@@ -11399,15 +11380,15 @@
       </c>
     </row>
     <row r="150" spans="1:7">
-      <c r="A150" s="147" t="s">
+      <c r="A150" s="216" t="s">
         <v>488</v>
       </c>
-      <c r="B150" s="148"/>
-      <c r="C150" s="148"/>
-      <c r="D150" s="148"/>
-      <c r="E150" s="148"/>
-      <c r="F150" s="148"/>
-      <c r="G150" s="149"/>
+      <c r="B150" s="217"/>
+      <c r="C150" s="217"/>
+      <c r="D150" s="217"/>
+      <c r="E150" s="217"/>
+      <c r="F150" s="217"/>
+      <c r="G150" s="218"/>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="130">
@@ -11640,15 +11621,15 @@
       </c>
     </row>
     <row r="161" spans="1:7">
-      <c r="A161" s="147" t="s">
+      <c r="A161" s="216" t="s">
         <v>488</v>
       </c>
-      <c r="B161" s="148"/>
-      <c r="C161" s="148"/>
-      <c r="D161" s="148"/>
-      <c r="E161" s="148"/>
-      <c r="F161" s="148"/>
-      <c r="G161" s="149"/>
+      <c r="B161" s="217"/>
+      <c r="C161" s="217"/>
+      <c r="D161" s="217"/>
+      <c r="E161" s="217"/>
+      <c r="F161" s="217"/>
+      <c r="G161" s="218"/>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="130">
@@ -11881,15 +11862,15 @@
       </c>
     </row>
     <row r="172" spans="1:7">
-      <c r="A172" s="147" t="s">
+      <c r="A172" s="216" t="s">
         <v>488</v>
       </c>
-      <c r="B172" s="148"/>
-      <c r="C172" s="148"/>
-      <c r="D172" s="148"/>
-      <c r="E172" s="148"/>
-      <c r="F172" s="148"/>
-      <c r="G172" s="149"/>
+      <c r="B172" s="217"/>
+      <c r="C172" s="217"/>
+      <c r="D172" s="217"/>
+      <c r="E172" s="217"/>
+      <c r="F172" s="217"/>
+      <c r="G172" s="218"/>
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="130">
@@ -12122,15 +12103,15 @@
       </c>
     </row>
     <row r="183" spans="1:7">
-      <c r="A183" s="147" t="s">
+      <c r="A183" s="216" t="s">
         <v>488</v>
       </c>
-      <c r="B183" s="148"/>
-      <c r="C183" s="148"/>
-      <c r="D183" s="148"/>
-      <c r="E183" s="148"/>
-      <c r="F183" s="148"/>
-      <c r="G183" s="149"/>
+      <c r="B183" s="217"/>
+      <c r="C183" s="217"/>
+      <c r="D183" s="217"/>
+      <c r="E183" s="217"/>
+      <c r="F183" s="217"/>
+      <c r="G183" s="218"/>
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="134">
@@ -12431,7 +12412,7 @@
       <c r="B3" t="s">
         <v>63</v>
       </c>
-      <c r="D3" s="224" t="s">
+      <c r="D3" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12461,16 +12442,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="164" t="s">
+      <c r="A1" s="156" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="165"/>
-      <c r="C1" s="165"/>
-      <c r="D1" s="165"/>
-      <c r="E1" s="165"/>
-      <c r="F1" s="165"/>
-      <c r="G1" s="166"/>
-      <c r="H1" s="227"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="226"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="93" t="s">
@@ -12485,12 +12466,12 @@
       <c r="D2" s="94" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="165" t="s">
+      <c r="E2" s="157" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="165"/>
-      <c r="G2" s="167"/>
-      <c r="H2" s="227"/>
+      <c r="F2" s="157"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="226"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="90">
@@ -12505,10 +12486,10 @@
       <c r="D3" s="91" t="s">
         <v>75</v>
       </c>
-      <c r="E3" s="168"/>
-      <c r="F3" s="168"/>
-      <c r="G3" s="169"/>
-      <c r="H3" s="227"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161"/>
+      <c r="H3" s="226"/>
     </row>
     <row r="4" spans="1:8" ht="64.5" customHeight="1">
       <c r="A4" s="90">
@@ -12523,24 +12504,24 @@
       <c r="D4" s="91" t="s">
         <v>78</v>
       </c>
-      <c r="E4" s="168" t="s">
+      <c r="E4" s="160" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="168"/>
-      <c r="G4" s="169"/>
-      <c r="H4" s="227"/>
+      <c r="F4" s="160"/>
+      <c r="G4" s="161"/>
+      <c r="H4" s="226"/>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A5" s="170" t="s">
+      <c r="A5" s="162" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="171"/>
-      <c r="C5" s="171"/>
-      <c r="D5" s="171"/>
-      <c r="E5" s="171"/>
-      <c r="F5" s="171"/>
-      <c r="G5" s="172"/>
-      <c r="H5" s="227"/>
+      <c r="B5" s="163"/>
+      <c r="C5" s="163"/>
+      <c r="D5" s="163"/>
+      <c r="E5" s="163"/>
+      <c r="F5" s="163"/>
+      <c r="G5" s="164"/>
+      <c r="H5" s="226"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="93" t="s">
@@ -12564,7 +12545,7 @@
       <c r="G6" s="94" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="227"/>
+      <c r="H6" s="226"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="90">
@@ -12588,7 +12569,7 @@
       <c r="G7" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H7" s="227"/>
+      <c r="H7" s="226"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="90">
@@ -12612,7 +12593,7 @@
       <c r="G8" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H8" s="227"/>
+      <c r="H8" s="226"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="90">
@@ -12636,7 +12617,7 @@
       <c r="G9" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H9" s="227"/>
+      <c r="H9" s="226"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="90">
@@ -12660,7 +12641,7 @@
       <c r="G10" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H10" s="227"/>
+      <c r="H10" s="226"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="90">
@@ -12684,7 +12665,7 @@
       <c r="G11" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H11" s="227"/>
+      <c r="H11" s="226"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="90">
@@ -12708,7 +12689,7 @@
       <c r="G12" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H12" s="227"/>
+      <c r="H12" s="226"/>
     </row>
     <row r="13" spans="1:8" ht="60.75">
       <c r="A13" s="90">
@@ -12732,7 +12713,7 @@
       <c r="G13" s="91" t="s">
         <v>107</v>
       </c>
-      <c r="H13" s="227"/>
+      <c r="H13" s="226"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="90">
@@ -12756,7 +12737,7 @@
       <c r="G14" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H14" s="227"/>
+      <c r="H14" s="226"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="90">
@@ -12780,7 +12761,7 @@
       <c r="G15" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H15" s="227"/>
+      <c r="H15" s="226"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="90">
@@ -12804,7 +12785,7 @@
       <c r="G16" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H16" s="227"/>
+      <c r="H16" s="226"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="90">
@@ -12828,7 +12809,7 @@
       <c r="G17" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H17" s="227"/>
+      <c r="H17" s="226"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="90">
@@ -12852,7 +12833,7 @@
       <c r="G18" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H18" s="227"/>
+      <c r="H18" s="226"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="90">
@@ -12876,7 +12857,7 @@
       <c r="G19" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H19" s="227"/>
+      <c r="H19" s="226"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="90">
@@ -12900,7 +12881,7 @@
       <c r="G20" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H20" s="227"/>
+      <c r="H20" s="226"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="90">
@@ -12924,7 +12905,7 @@
       <c r="G21" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H21" s="227"/>
+      <c r="H21" s="226"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="90">
@@ -12948,7 +12929,7 @@
       <c r="G22" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H22" s="227"/>
+      <c r="H22" s="226"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="90">
@@ -12972,7 +12953,7 @@
       <c r="G23" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H23" s="227"/>
+      <c r="H23" s="226"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="90">
@@ -12996,7 +12977,7 @@
       <c r="G24" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H24" s="227"/>
+      <c r="H24" s="226"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="90">
@@ -13020,7 +13001,7 @@
       <c r="G25" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H25" s="227"/>
+      <c r="H25" s="226"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="90">
@@ -13044,7 +13025,7 @@
       <c r="G26" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H26" s="227"/>
+      <c r="H26" s="226"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="90">
@@ -13068,7 +13049,7 @@
       <c r="G27" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H27" s="227"/>
+      <c r="H27" s="226"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="90">
@@ -13092,7 +13073,7 @@
       <c r="G28" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H28" s="227"/>
+      <c r="H28" s="226"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="90">
@@ -13116,7 +13097,7 @@
       <c r="G29" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H29" s="227"/>
+      <c r="H29" s="226"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="90">
@@ -13140,7 +13121,7 @@
       <c r="G30" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H30" s="227"/>
+      <c r="H30" s="226"/>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="90">
@@ -13164,7 +13145,7 @@
       <c r="G31" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H31" s="227"/>
+      <c r="H31" s="226"/>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="90">
@@ -13188,7 +13169,7 @@
       <c r="G32" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H32" s="227"/>
+      <c r="H32" s="226"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="90">
@@ -13212,7 +13193,7 @@
       <c r="G33" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H33" s="227"/>
+      <c r="H33" s="226"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="90">
@@ -13236,7 +13217,7 @@
       <c r="G34" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H34" s="227"/>
+      <c r="H34" s="226"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="90">
@@ -13260,7 +13241,7 @@
       <c r="G35" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H35" s="227"/>
+      <c r="H35" s="226"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="90">
@@ -13284,7 +13265,7 @@
       <c r="G36" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H36" s="227"/>
+      <c r="H36" s="226"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="90">
@@ -13308,7 +13289,7 @@
       <c r="G37" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H37" s="227"/>
+      <c r="H37" s="226"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="90">
@@ -13332,7 +13313,7 @@
       <c r="G38" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H38" s="227"/>
+      <c r="H38" s="226"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="90">
@@ -13356,7 +13337,7 @@
       <c r="G39" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H39" s="227"/>
+      <c r="H39" s="226"/>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="90">
@@ -13380,7 +13361,7 @@
       <c r="G40" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H40" s="227"/>
+      <c r="H40" s="226"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="90">
@@ -13404,7 +13385,7 @@
       <c r="G41" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H41" s="227"/>
+      <c r="H41" s="226"/>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="90">
@@ -13428,7 +13409,7 @@
       <c r="G42" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H42" s="227"/>
+      <c r="H42" s="226"/>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="90">
@@ -13452,7 +13433,7 @@
       <c r="G43" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H43" s="227"/>
+      <c r="H43" s="226"/>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="90">
@@ -13476,7 +13457,7 @@
       <c r="G44" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H44" s="227"/>
+      <c r="H44" s="226"/>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="90">
@@ -13500,7 +13481,7 @@
       <c r="G45" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H45" s="227"/>
+      <c r="H45" s="226"/>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="90">
@@ -13524,7 +13505,7 @@
       <c r="G46" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H46" s="227"/>
+      <c r="H46" s="226"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="90">
@@ -13548,7 +13529,7 @@
       <c r="G47" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H47" s="227"/>
+      <c r="H47" s="226"/>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="90">
@@ -13572,7 +13553,7 @@
       <c r="G48" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H48" s="227"/>
+      <c r="H48" s="226"/>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="90">
@@ -13596,7 +13577,7 @@
       <c r="G49" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H49" s="227"/>
+      <c r="H49" s="226"/>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="90">
@@ -13620,7 +13601,7 @@
       <c r="G50" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H50" s="227"/>
+      <c r="H50" s="226"/>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="90">
@@ -13644,7 +13625,7 @@
       <c r="G51" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H51" s="227"/>
+      <c r="H51" s="226"/>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="90">
@@ -13668,7 +13649,7 @@
       <c r="G52" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H52" s="227"/>
+      <c r="H52" s="226"/>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="90">
@@ -13692,7 +13673,7 @@
       <c r="G53" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H53" s="227"/>
+      <c r="H53" s="226"/>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="90">
@@ -13716,7 +13697,7 @@
       <c r="G54" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H54" s="227"/>
+      <c r="H54" s="226"/>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="90">
@@ -13740,7 +13721,7 @@
       <c r="G55" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H55" s="227"/>
+      <c r="H55" s="226"/>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="90">
@@ -13764,7 +13745,7 @@
       <c r="G56" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H56" s="227"/>
+      <c r="H56" s="226"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="90">
@@ -13788,7 +13769,7 @@
       <c r="G57" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="H57" s="227"/>
+      <c r="H57" s="226"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="114">
@@ -13812,137 +13793,137 @@
       <c r="G58" s="115" t="s">
         <v>92</v>
       </c>
-      <c r="H58" s="227"/>
+      <c r="H58" s="226"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="228">
+      <c r="A59" s="227">
         <v>53</v>
       </c>
-      <c r="B59" s="226" t="s">
+      <c r="B59" s="225" t="s">
         <v>87</v>
       </c>
-      <c r="C59" s="229" t="s">
+      <c r="C59" s="228" t="s">
         <v>200</v>
       </c>
-      <c r="D59" s="230" t="s">
-        <v>89</v>
-      </c>
-      <c r="E59" s="231" t="s">
-        <v>90</v>
-      </c>
-      <c r="F59" s="226" t="s">
+      <c r="D59" s="229" t="s">
+        <v>89</v>
+      </c>
+      <c r="E59" s="230" t="s">
+        <v>90</v>
+      </c>
+      <c r="F59" s="225" t="s">
         <v>201</v>
       </c>
-      <c r="G59" s="226" t="s">
+      <c r="G59" s="225" t="s">
         <v>92</v>
       </c>
-      <c r="H59" s="227"/>
+      <c r="H59" s="226"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="228">
+      <c r="A60" s="227">
         <v>54</v>
       </c>
-      <c r="B60" s="226" t="s">
+      <c r="B60" s="225" t="s">
         <v>87</v>
       </c>
-      <c r="C60" s="229" t="s">
+      <c r="C60" s="228" t="s">
         <v>202</v>
       </c>
-      <c r="D60" s="230" t="s">
-        <v>89</v>
-      </c>
-      <c r="E60" s="231" t="s">
-        <v>90</v>
-      </c>
-      <c r="F60" s="226" t="s">
+      <c r="D60" s="229" t="s">
+        <v>89</v>
+      </c>
+      <c r="E60" s="230" t="s">
+        <v>90</v>
+      </c>
+      <c r="F60" s="225" t="s">
         <v>203</v>
       </c>
-      <c r="G60" s="226" t="s">
+      <c r="G60" s="225" t="s">
         <v>92</v>
       </c>
-      <c r="H60" s="227"/>
+      <c r="H60" s="226"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="228">
+      <c r="A61" s="227">
         <v>55</v>
       </c>
-      <c r="B61" s="226" t="s">
+      <c r="B61" s="225" t="s">
         <v>87</v>
       </c>
-      <c r="C61" s="229" t="s">
+      <c r="C61" s="228" t="s">
         <v>204</v>
       </c>
-      <c r="D61" s="230" t="s">
-        <v>89</v>
-      </c>
-      <c r="E61" s="231" t="s">
-        <v>90</v>
-      </c>
-      <c r="F61" s="226" t="s">
+      <c r="D61" s="229" t="s">
+        <v>89</v>
+      </c>
+      <c r="E61" s="230" t="s">
+        <v>90</v>
+      </c>
+      <c r="F61" s="225" t="s">
         <v>205</v>
       </c>
-      <c r="G61" s="226" t="s">
+      <c r="G61" s="225" t="s">
         <v>92</v>
       </c>
-      <c r="H61" s="227"/>
+      <c r="H61" s="226"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="228">
+      <c r="A62" s="227">
         <v>56</v>
       </c>
-      <c r="B62" s="226" t="s">
+      <c r="B62" s="225" t="s">
         <v>87</v>
       </c>
-      <c r="C62" s="229" t="s">
+      <c r="C62" s="228" t="s">
         <v>206</v>
       </c>
-      <c r="D62" s="230" t="s">
+      <c r="D62" s="229" t="s">
         <v>122</v>
       </c>
-      <c r="E62" s="231" t="s">
-        <v>90</v>
-      </c>
-      <c r="F62" s="226" t="s">
+      <c r="E62" s="230" t="s">
+        <v>90</v>
+      </c>
+      <c r="F62" s="225" t="s">
         <v>207</v>
       </c>
-      <c r="G62" s="226" t="s">
+      <c r="G62" s="225" t="s">
         <v>92</v>
       </c>
-      <c r="H62" s="227"/>
+      <c r="H62" s="226"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="228">
+      <c r="A63" s="227">
         <v>57</v>
       </c>
-      <c r="B63" s="226" t="s">
+      <c r="B63" s="225" t="s">
         <v>87</v>
       </c>
-      <c r="C63" s="229" t="s">
+      <c r="C63" s="228" t="s">
         <v>208</v>
       </c>
-      <c r="D63" s="230" t="s">
-        <v>89</v>
-      </c>
-      <c r="E63" s="231" t="s">
-        <v>90</v>
-      </c>
-      <c r="F63" s="226" t="s">
+      <c r="D63" s="229" t="s">
+        <v>89</v>
+      </c>
+      <c r="E63" s="230" t="s">
+        <v>90</v>
+      </c>
+      <c r="F63" s="225" t="s">
         <v>209</v>
       </c>
-      <c r="G63" s="226" t="s">
+      <c r="G63" s="225" t="s">
         <v>92</v>
       </c>
-      <c r="H63" s="227"/>
+      <c r="H63" s="226"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="232"/>
-      <c r="B64" s="227"/>
-      <c r="C64" s="232"/>
-      <c r="D64" s="232"/>
-      <c r="E64" s="227"/>
-      <c r="F64" s="227"/>
-      <c r="G64" s="227"/>
-      <c r="H64" s="233"/>
+      <c r="A64" s="231"/>
+      <c r="B64" s="226"/>
+      <c r="C64" s="231"/>
+      <c r="D64" s="231"/>
+      <c r="E64" s="226"/>
+      <c r="F64" s="226"/>
+      <c r="G64" s="226"/>
+      <c r="H64" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -13970,14 +13951,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="165" t="s">
         <v>210</v>
       </c>
-      <c r="B1" s="174"/>
-      <c r="C1" s="174"/>
-      <c r="D1" s="174"/>
-      <c r="E1" s="174"/>
-      <c r="F1" s="174"/>
+      <c r="B1" s="166"/>
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
@@ -13987,10 +13968,10 @@
       <c r="B2" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="175" t="s">
+      <c r="C2" s="167" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="176"/>
+      <c r="D2" s="168"/>
       <c r="E2" s="40" t="s">
         <v>71</v>
       </c>
@@ -14006,10 +13987,10 @@
       <c r="B3" s="41" t="s">
         <v>211</v>
       </c>
-      <c r="C3" s="177" t="s">
+      <c r="C3" s="169" t="s">
         <v>212</v>
       </c>
-      <c r="D3" s="178"/>
+      <c r="D3" s="170"/>
       <c r="E3" s="41" t="s">
         <v>75</v>
       </c>
@@ -14025,10 +14006,10 @@
       <c r="B4" s="41" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="177" t="s">
+      <c r="C4" s="169" t="s">
         <v>214</v>
       </c>
-      <c r="D4" s="178"/>
+      <c r="D4" s="170"/>
       <c r="E4" s="41" t="s">
         <v>78</v>
       </c>
@@ -14037,14 +14018,14 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="174" t="s">
+      <c r="A5" s="166" t="s">
         <v>216</v>
       </c>
-      <c r="B5" s="174"/>
-      <c r="C5" s="174"/>
-      <c r="D5" s="174"/>
-      <c r="E5" s="174"/>
-      <c r="F5" s="174"/>
+      <c r="B5" s="166"/>
+      <c r="C5" s="166"/>
+      <c r="D5" s="166"/>
+      <c r="E5" s="166"/>
+      <c r="F5" s="166"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="40" t="s">
@@ -14174,14 +14155,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24.75" customHeight="1">
-      <c r="A1" s="179" t="s">
+      <c r="A1" s="171" t="s">
         <v>233</v>
       </c>
-      <c r="B1" s="180"/>
-      <c r="C1" s="180"/>
-      <c r="D1" s="180"/>
-      <c r="E1" s="180"/>
-      <c r="F1" s="180"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
     </row>
     <row r="2" spans="1:6" ht="24.75" customHeight="1">
       <c r="A2" s="46" t="s">
@@ -14190,10 +14171,10 @@
       <c r="B2" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="181" t="s">
+      <c r="C2" s="173" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="182"/>
+      <c r="D2" s="174"/>
       <c r="E2" s="46" t="s">
         <v>71</v>
       </c>
@@ -14208,10 +14189,10 @@
       <c r="B3" s="48" t="s">
         <v>234</v>
       </c>
-      <c r="C3" s="183" t="s">
+      <c r="C3" s="175" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="184"/>
+      <c r="D3" s="176"/>
       <c r="E3" s="47" t="s">
         <v>75</v>
       </c>
@@ -14224,10 +14205,10 @@
       <c r="B4" s="50" t="s">
         <v>235</v>
       </c>
-      <c r="C4" s="185" t="s">
+      <c r="C4" s="177" t="s">
         <v>236</v>
       </c>
-      <c r="D4" s="186"/>
+      <c r="D4" s="178"/>
       <c r="E4" s="49" t="s">
         <v>237</v>
       </c>
@@ -14236,22 +14217,22 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="24.75" customHeight="1">
-      <c r="A5" s="233"/>
-      <c r="B5" s="233"/>
-      <c r="C5" s="233"/>
-      <c r="D5" s="233"/>
-      <c r="E5" s="233"/>
-      <c r="F5" s="233"/>
+      <c r="A5" s="232"/>
+      <c r="B5" s="232"/>
+      <c r="C5" s="232"/>
+      <c r="D5" s="232"/>
+      <c r="E5" s="232"/>
+      <c r="F5" s="232"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="181" t="s">
+      <c r="A7" s="173" t="s">
         <v>239</v>
       </c>
-      <c r="B7" s="187"/>
-      <c r="C7" s="187"/>
-      <c r="D7" s="187"/>
-      <c r="E7" s="187"/>
-      <c r="F7" s="233"/>
+      <c r="B7" s="179"/>
+      <c r="C7" s="179"/>
+      <c r="D7" s="179"/>
+      <c r="E7" s="179"/>
+      <c r="F7" s="232"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="46" t="s">
@@ -14269,7 +14250,7 @@
       <c r="E8" s="46" t="s">
         <v>220</v>
       </c>
-      <c r="F8" s="233"/>
+      <c r="F8" s="232"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="51" t="s">
@@ -14287,7 +14268,7 @@
       <c r="E9" s="54" t="s">
         <v>241</v>
       </c>
-      <c r="F9" s="233"/>
+      <c r="F9" s="232"/>
     </row>
     <row r="10" spans="1:6" ht="60.75">
       <c r="A10" s="51" t="s">
@@ -14305,7 +14286,7 @@
       <c r="E10" s="54" t="s">
         <v>243</v>
       </c>
-      <c r="F10" s="233"/>
+      <c r="F10" s="232"/>
     </row>
     <row r="11" spans="1:6" ht="91.5">
       <c r="A11" s="51" t="s">
@@ -14323,7 +14304,7 @@
       <c r="E11" s="54" t="s">
         <v>246</v>
       </c>
-      <c r="F11" s="233"/>
+      <c r="F11" s="232"/>
     </row>
     <row r="12" spans="1:6" ht="121.5">
       <c r="A12" s="51" t="s">
@@ -14341,7 +14322,7 @@
       <c r="E12" s="54" t="s">
         <v>249</v>
       </c>
-      <c r="F12" s="233"/>
+      <c r="F12" s="232"/>
     </row>
     <row r="13" spans="1:6" ht="76.5">
       <c r="A13" s="51" t="s">
@@ -14359,7 +14340,7 @@
       <c r="E13" s="54" t="s">
         <v>251</v>
       </c>
-      <c r="F13" s="233"/>
+      <c r="F13" s="232"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="51" t="s">
@@ -14377,7 +14358,7 @@
       <c r="E14" s="54" t="s">
         <v>254</v>
       </c>
-      <c r="F14" s="233"/>
+      <c r="F14" s="232"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="51" t="s">
@@ -14395,7 +14376,7 @@
       <c r="E15" s="54" t="s">
         <v>256</v>
       </c>
-      <c r="F15" s="233"/>
+      <c r="F15" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -14422,13 +14403,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="190" t="s">
+      <c r="A1" s="182" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="191"/>
-      <c r="C1" s="191"/>
-      <c r="D1" s="191"/>
-      <c r="E1" s="192"/>
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="184"/>
       <c r="F1" s="5"/>
     </row>
     <row r="2" spans="1:6">
@@ -14529,39 +14510,39 @@
       <c r="E7" s="30"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1">
-      <c r="A8" s="190" t="s">
+      <c r="A8" s="182" t="s">
         <v>266</v>
       </c>
-      <c r="B8" s="191"/>
-      <c r="C8" s="191"/>
-      <c r="D8" s="191"/>
-      <c r="E8" s="191"/>
+      <c r="B8" s="183"/>
+      <c r="C8" s="183"/>
+      <c r="D8" s="183"/>
+      <c r="E8" s="183"/>
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="193" t="s">
+      <c r="A9" s="185" t="s">
         <v>267</v>
       </c>
-      <c r="B9" s="194" t="s">
+      <c r="B9" s="186" t="s">
         <v>268</v>
       </c>
-      <c r="C9" s="194" t="s">
+      <c r="C9" s="186" t="s">
         <v>219</v>
       </c>
-      <c r="D9" s="195" t="s">
+      <c r="D9" s="187" t="s">
         <v>220</v>
       </c>
-      <c r="E9" s="195" t="s">
+      <c r="E9" s="187" t="s">
         <v>269</v>
       </c>
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="193"/>
-      <c r="B10" s="194"/>
-      <c r="C10" s="194"/>
-      <c r="D10" s="196"/>
-      <c r="E10" s="196"/>
+      <c r="A10" s="185"/>
+      <c r="B10" s="186"/>
+      <c r="C10" s="186"/>
+      <c r="D10" s="188"/>
+      <c r="E10" s="188"/>
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6">
@@ -15591,13 +15572,13 @@
       <c r="F67" s="5"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="188" t="s">
+      <c r="A68" s="180" t="s">
         <v>286</v>
       </c>
-      <c r="B68" s="189"/>
-      <c r="C68" s="189"/>
-      <c r="D68" s="189"/>
-      <c r="E68" s="189"/>
+      <c r="B68" s="181"/>
+      <c r="C68" s="181"/>
+      <c r="D68" s="181"/>
+      <c r="E68" s="181"/>
       <c r="F68" s="5"/>
     </row>
     <row r="69" spans="1:6">
@@ -16646,13 +16627,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="197" t="s">
+      <c r="A1" s="189" t="s">
         <v>315</v>
       </c>
-      <c r="B1" s="198"/>
-      <c r="C1" s="198"/>
-      <c r="D1" s="198"/>
-      <c r="E1" s="199"/>
+      <c r="B1" s="190"/>
+      <c r="C1" s="190"/>
+      <c r="D1" s="190"/>
+      <c r="E1" s="191"/>
       <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:6">
@@ -16699,13 +16680,13 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="200" t="s">
+      <c r="A5" s="192" t="s">
         <v>318</v>
       </c>
-      <c r="B5" s="200"/>
-      <c r="C5" s="200"/>
-      <c r="D5" s="200"/>
-      <c r="E5" s="200"/>
+      <c r="B5" s="192"/>
+      <c r="C5" s="192"/>
+      <c r="D5" s="192"/>
+      <c r="E5" s="192"/>
       <c r="F5" s="106"/>
     </row>
     <row r="6" spans="1:6">
@@ -16888,13 +16869,13 @@
       <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="201" t="s">
+      <c r="A5" s="193" t="s">
         <v>266</v>
       </c>
-      <c r="B5" s="201"/>
-      <c r="C5" s="201"/>
-      <c r="D5" s="201"/>
-      <c r="E5" s="201"/>
+      <c r="B5" s="193"/>
+      <c r="C5" s="193"/>
+      <c r="D5" s="193"/>
+      <c r="E5" s="193"/>
     </row>
     <row r="6" spans="1:5" ht="24.75">
       <c r="A6" s="21" t="s">
@@ -17082,8 +17063,8 @@
       </c>
       <c r="B6" s="58"/>
       <c r="C6" s="58"/>
-      <c r="D6" s="204"/>
-      <c r="E6" s="204"/>
+      <c r="D6" s="196"/>
+      <c r="E6" s="196"/>
       <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" ht="21" customHeight="1">
@@ -17096,10 +17077,10 @@
       <c r="C7" s="59" t="s">
         <v>219</v>
       </c>
-      <c r="D7" s="205" t="s">
+      <c r="D7" s="197" t="s">
         <v>220</v>
       </c>
-      <c r="E7" s="206"/>
+      <c r="E7" s="198"/>
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" ht="21" customHeight="1">
@@ -17112,10 +17093,10 @@
       <c r="C8" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="202" t="s">
+      <c r="D8" s="194" t="s">
         <v>344</v>
       </c>
-      <c r="E8" s="203"/>
+      <c r="E8" s="195"/>
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" ht="21" customHeight="1">
@@ -17128,10 +17109,10 @@
       <c r="C9" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="202" t="s">
+      <c r="D9" s="194" t="s">
         <v>156</v>
       </c>
-      <c r="E9" s="203"/>
+      <c r="E9" s="195"/>
       <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:7" ht="14.45" customHeight="1">
@@ -17144,10 +17125,10 @@
       <c r="C10" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="202" t="s">
+      <c r="D10" s="194" t="s">
         <v>142</v>
       </c>
-      <c r="E10" s="203"/>
+      <c r="E10" s="195"/>
     </row>
     <row r="11" spans="1:7" ht="14.45" customHeight="1">
       <c r="A11" s="8" t="s">
@@ -17159,10 +17140,10 @@
       <c r="C11" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="202" t="s">
+      <c r="D11" s="194" t="s">
         <v>144</v>
       </c>
-      <c r="E11" s="203"/>
+      <c r="E11" s="195"/>
     </row>
     <row r="12" spans="1:7" ht="14.45" customHeight="1">
       <c r="A12" s="8" t="s">
@@ -17174,10 +17155,10 @@
       <c r="C12" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="202" t="s">
+      <c r="D12" s="194" t="s">
         <v>346</v>
       </c>
-      <c r="E12" s="203"/>
+      <c r="E12" s="195"/>
     </row>
     <row r="13" spans="1:7" ht="14.45" customHeight="1">
       <c r="A13" s="8" t="s">
@@ -17189,10 +17170,10 @@
       <c r="C13" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="202" t="s">
+      <c r="D13" s="194" t="s">
         <v>103</v>
       </c>
-      <c r="E13" s="203"/>
+      <c r="E13" s="195"/>
     </row>
     <row r="14" spans="1:7" ht="70.5" customHeight="1">
       <c r="A14" s="8" t="s">
@@ -17204,10 +17185,10 @@
       <c r="C14" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D14" s="202" t="s">
+      <c r="D14" s="194" t="s">
         <v>348</v>
       </c>
-      <c r="E14" s="203"/>
+      <c r="E14" s="195"/>
     </row>
     <row r="15" spans="1:7" ht="14.45" customHeight="1"/>
   </sheetData>
